--- a/fuzzing-security-testing/BaoCaoATPM/Module_Orders_Create_spec.xlsx
+++ b/fuzzing-security-testing/BaoCaoATPM/Module_Orders_Create_spec.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="2" min="1" max="1"/>
@@ -473,7 +473,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="175.4" customHeight="1" s="6">
+    <row r="3" ht="114" customHeight="1" s="6">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>description</t>
@@ -481,7 +481,115 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Đặc tả yêu cầu module ORD của hệ thống bán hàng. API được kiểm thử trên node_harness với datastore trong bộ nhớ; các request có thể chạy đồng thời. Cụm khóa và hàm C/Python/SMT là mô hình kiểm chứng minh họa theo template, gồm lỗi cấy có chủ đích; không phải bằng chứng lỗi bộ nhớ của Node.js. Đây là hợp đồng mong đợi để xây dựng testcase; mức đáp ứng của code được đánh giá riêng, không khẳng định mọi yêu cầu đã triển khai.</t>
+          <t>Đặc tả hợp đồng an toàn module ORD trên hệ thống bán hàng mô phỏng node_harness. Request và code xử lý chạy thực; datastore/dịch vụ là test double. Yêu cầu mong đợi không đồng nghĩa code hiện đã đáp ứng. Giữ đủ 10 sheet và ID testcase; kết quả quan sát lưu riêng trong report/evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150.4" customHeight="1" s="6">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>pham_vi_chinh</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Blackbox: seed → đột biến → HTTP → oracle. Khảo sát coverage: replay/lân cận → giữ input mở thêm dòng; đây là coverage-guided/greybox. Module này có 8 testcase API được campaign hiện tại thực thi: TC-ORD-1, TC-ORD-2, TC-ORD-3, TC-ORD-4, TC-ORD-5, TC-ORD-6, TC-ORD-18, TC-ORD-19. Oracle hiện chỉ kiểm tra các điều kiện đã cài đặt, không bao phủ mọi yêu cầu mở rộng trong Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="130.4" customHeight="1" s="6">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>pham_vi_bo_tro</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Toàn bộ 5 Excel có 134 testcase; campaign API có 29 testcase/59 kịch bản khi fuzz-cases=8; 105 testcase còn lại được ghi riêng trong excluded_testcases.json, chưa thực thi trong campaign. Race/version, timing, bộ đếm, CTL, mẫu C/Python và mô hình số học được giữ làm đặc tả bổ sung; chưa tuyên bố đã chạy/kiểm chứng lại đầy đủ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1" s="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>thu_tu_testcase</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>API an toàn đầu vào/quyền/trạng thái → tái hiện và phân loại bằng chứng → mẫu ngoại lệ/bộ nhớ độc lập → concurrency/timing/số học → seed đối chứng. Trong từng nhóm: HIGH, MEDIUM, LOW. ID không thay đổi; kết quả thực tế lưu ở report, không điền vào KetQuaMongDoi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="127.2" customHeight="1" s="6">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>phuong_phap_whitebox</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Concolic có chọn lọc cho TC-ORD-3/4: POST /api/orders → OrderModel.save → castNumberOrThrow(totalAmount). Mô hình thủ công total_kind 0..7; trace nhánh thật → giữ tiền tố/phủ định nhánh → Z3 → JSON → API xác nhận. Các trường khác dùng seed hợp lệ. Không tự symbolic toàn bộ JavaScript, không giải mọi giá trị số/chuỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="124.8" customHeight="1" s="6">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>pham_vi_mo_hinh</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>MoHinhTrangThai/ThuocTinhAnToan/LoaiTruLanNhau mô tả thuộc tính thiết kế, chưa xác minh CTL trong bộ chạy hiện tại. HamSinhMa chứa thiết kế mẫu minh họa C/Python; KiemTraSoHoc là mô hình số học độc lập theo giả định, không phải path condition của concolic. Không tự đồng nhất mô hình int32 với Number JavaScript.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="131.6" customHeight="1" s="6">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>bang_chung_ket_luan</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 5xx là lỗi phản hồi ứng dụng; timeout là nghi vấn hang. Crash cần log và mã thoát/signal; lỗi bộ nhớ cần chẩn đoán instrumentation phù hợp. SAT/UNSAT/unknown phải lưu công thức và phạm vi; không mặc định SAT, không coi unknown là UNSAT. Không điền kết quả chạy vào KetQuaMongDoi hoặc dùng finding occurrences làm số lỗi gốc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="126" customHeight="1" s="6">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>lenh_chay</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Tại thư mục gốc: python fuzzing-security-testing/fuzzers/run_ch4.py --seed 7 --fuzz-cases 8. Demo có concolic riêng: python fuzzing-security-testing/fuzzers/run_fuzzing.py --iterations 42 --iterations-per-case 8 --max-cases 2 --seed 7 --concolic. Hai chế độ lưu report riêng, không tự thực thi toàn bộ 134 testcase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="104.8" customHeight="1" s="6">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>bao_phu_thuc_thi</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá theo snapshot/hash trong từng report, không tái gán kết quả cũ cho Excel đã sửa. Bộ concolic đối chiếu mô hình với 8 đại diện trong test hồi quy; chiến dịch solver không bắt buộc chạy đủ 8 đại diện. Chưa có sanitizer hoặc bảo đảm coverage toàn hệ thống.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bo_sung_runtime</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bổ sung TC-ORD-22 đến TC-ORD-27: discovery, native memory, leak, crash/hang, replay, minimization/dedup. Đây là đặc tả chưa có runner tự động; không thay đổi phạm vi 29 testcase API đã có code. Tổng 134 testcase/105 ngoài campaign theo bộ Excel mới; report/snapshot cũ vẫn thuộc phiên bản 104 testcase, không tái gán số liệu.</t>
         </is>
       </c>
     </row>
@@ -496,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="34.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.88671875" customWidth="1" style="2" min="1" max="1"/>
@@ -558,7 +666,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>products sai kiểu dữ liệu vẫn được chấp nhận</t>
+          <t>Sai kiểu và cấu trúc giỏ hàng đi vào tầng xử lý đơn</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -569,12 +677,13 @@
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Gửi products: {} (object rỗng)
-Gửi products: 'abc' (chuỗi)</t>
+Gửi products: 'abc' (chuỗi)
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>ĐÃ XÁC NHẬN THỰC NGHIỆM: cả 2 trả về 200 - VI PHẠM. Oracle fuzzer hiện CHƯA phát hiện được lỗi này</t>
+          <t>HTTP 400/422 cho products sai cấu trúc hoặc số lượng âm; không coi đơn sai cấu trúc là đơn hợp lệ.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -596,7 +705,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Thiếu từng trường trong shippingInfo</t>
+          <t>Thiếu cấu trúc lồng shippingInfo gây ngoại lệ</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -608,12 +717,13 @@
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Xóa lần lượt shippingInfo/fullName/phone/address
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
+3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Cả 4 trường hợp trả về 400</t>
+          <t>HTTP 400 khi thiếu shippingInfo hoặc trường bắt buộc; không phát sinh ngoại lệ chưa xử lý.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -622,7 +732,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="283.2" customHeight="1" s="6">
+    <row r="4" ht="300" customHeight="1" s="6">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TC-ORD-3</t>
@@ -635,24 +745,25 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Thiếu totalAmount</t>
+          <t>Xử lý an toàn totalAmount thiếu/null và xác nhận nhánh required</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Đã đăng nhập, có token, cart/shipping hợp lệ</t>
+          <t>Harness node_harness chạy được; seed_order_valid.json tạo đơn hợp lệ, có token và catalog/shipping hợp lệ. Phần concolic cần z3-solver trong requirements.txt; chạy từ thư mục gốc. Không cần MongoDB/production.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Gửi đơn hàng, xóa trường totalAmount
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
+          <t>A. Kịch bản API: giữ seed hợp lệ, xóa totalAmount; gửi POST /api/orders bằng token hợp lệ, lưu response.
+B. Concolic: chạy python fuzzing-security-testing/fuzzers/whitebox_fuzzer.py --concolic --iterations-per-target 12. Bắt đầu totalAmount=400000; thu branch_trace thật tại OrderModel.save.
+Giữ tiền tố và phủ định order.total.required từ false sang true; Z3 có thể chọn đại diện null hoặc missing. Lưu công thức/model, giải mã thành JSON và gửi lại API. Đối chiếu nhánh required=true với tiền tố đã giải. Không bắt buộc solver chọn cả null và missing trong một lần chạy.
+Xem concolic/report.json và evidence: input, result.branch_trace, orders_created, violations và replay. Phân biệt lỗi ứng dụng với lỗi setup, timeout hoặc tiến trình kết thúc bất thường.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ĐÃ XÁC NHẬN: trả về 500 (không phải 400) - VI PHẠM</t>
+          <t>Yêu cầu ứng dụng: thiếu/null trả HTTP 400 có kiểm soát, không tạo đơn; HTTP 500 là vi phạm xử lý lỗi đầu vào, chưa chứng minh crash/bộ nhớ. Yêu cầu công cụ concolic: SAT phải sinh input có tiền tố nhánh thực đo đúng với model; lệch mô hình/trace phải báo lỗi công cụ, không ghi xác nhận nhánh thành công. Input vi phạm được replay từ dữ liệu sạch và lưu kết quả. Chưa chạy hoặc không có bằng chứng thì chưa xác minh.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -661,7 +772,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="314" customHeight="1" s="6">
+    <row r="5" ht="300" customHeight="1" s="6">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TC-ORD-4</t>
@@ -674,24 +785,26 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>totalAmount sai kiểu dữ liệu</t>
+          <t>Sai kiểu totalAmount: mutation và concolic xác nhận đường ép kiểu</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Đã đăng nhập, có token</t>
+          <t>Đăng nhập thành công, seed đơn hợp lệ, catalog/shipping giữ cố định. Cài z3-solver; có thể chạy harness Node và đọc evidence. Chỉ biến đổi totalAmount trong phần concolic.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Gửi totalAmount là object/array/NaN, lặp lại bằng fuzzer
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
+          <t>A. Campaign API: thử totalAmount là object, array, chuỗi "NaN"/"Infinity" và các mutation đã khai báo; đây là chuỗi JSON, không phải literal NaN/Infinity ngoài chuẩn JSON.
+B. Chạy python fuzzing-security-testing/fuzzers/whitebox_fuzzer.py --concolic --iterations-per-target 12. Biến total_kind là Int từ 0 đến 7, lần lượt đại diện number=400000, numeric_string="400000", invalid_string="not-a-number", object={}, null, missing, boolean=true, array=[]. Các trường khác dùng seed hợp lệ.
+Lấy trace order.total.required, cast.empty, cast.number, cast.boolean, cast.invalid thực sự đi qua. Với mỗi nhánh được chọn, giữ tiền tố, phủ định nhánh và bỏ hậu tố cũ; giải bằng Z3 rồi gửi JSON mới qua POST /api/orders để xác nhận tiền tố.
+Lưu SAT/model, UNSAT hoặc unknown riêng; UNSAT chỉ áp dụng miền/prefix đã mã hóa. Trong tiền tố required=false, yêu cầu cast.empty=true là mâu thuẫn. Không coi UNSAT này là chứng minh API an toàn.
+Kiểm tra HTTP và orders_created; chạy lại input có vi phạm. Chiến dịch chọn đại diện để mở đường mới, không cam kết thử cả 8 đại diện; test hồi quy của công cụ đối chiếu cả 8 đại diện với nhánh Node.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Phần lớn trả về 500 - VI PHẠM. Ghi nhận 120-240 crash trên 1400-3500 lần thử</t>
+          <t>Yêu cầu ứng dụng: sai kiểu từ chối HTTP 400/422; không HTTP 5xx hoặc tạo đơn khi từ chối. Chuỗi số/boolean được chấp nhận qua ép kiểu là vi phạm hợp đồng kiểu, chưa tự chứng minh thiệt hại hoặc khả năng khai thác. Yêu cầu công cụ: model phải khớp trace và tiền tố mục tiêu; báo lỗi nếu lệch, không ghi xác nhận giả. UNKNOWN không được coi là UNSAT. Lưu điều kiện, input, response, trạng thái dữ liệu và replay; số input vi phạm không phải số lỗi gốc. Không suy ra lỗi bộ nhớ từ HTTP 500.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -713,7 +826,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>totalAmount lệch giá thật</t>
+          <t>Tin cậy giá từ client làm sai toàn vẹn đơn hàng</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -725,12 +838,13 @@
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Gửi totalAmount=400000, sản phẩm thật giá 200000 x1
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
+3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Server lưu nguyên 400000, trả 200 - VI PHẠM. 239/245 vi phạm lần chạy đầu là loại này</t>
+          <t>Server từ chối giá/tổng bị sửa hoặc tính lại từ catalog tin cậy; không lưu tổng bị giả mạo.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -752,7 +866,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>totalAmount âm</t>
+          <t>Giá trị âm vượt qua kiểm tra miền số tiền</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -764,522 +878,845 @@
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Gửi totalAmount = -999999999
+3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 400/422; không chấp nhận tổng tiền âm.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="375.6" customHeight="1" s="6">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-18</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-5</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Giả mạo đồng thời đơn giá và tổng tiền để vượt oracle</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Catalog productId=1 có giá 200000; actor hợp lệ. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1. Gửi sản phẩm price=1, quantity=2, totalAmount=2; đọc giá trị đơn đã lưu nếu thành công.
+2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
+Dữ liệu thử: {"products":[{"productId":1,"price":1,"quantity":2}],"totalAmount":2}
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Từ chối 400/422 hoặc tính lại từ catalog thành 400000 trong seed không phí/giảm giá; không lưu tổng 2.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="300" customHeight="1" s="6">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-20</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-FUZZ-20</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra quy trình fuzzing: Chuyển input blackbox sang khảo sát coverage</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Có report blackbox mới chứa target=orders, input và had_auth; target được hỗ trợ; dữ liệu harness được seed sạch. Chế độ --blackbox-report là coverage-guided, khác --concolic.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>1. Chọn input blackbox có triệu chứng, lưu đường dẫn report và trạng thái đã biết.
+2. Chạy whitebox_fuzzer.py với --blackbox-report &lt;report.json&gt; --iterations-per-target 12, không kết hợp --concolic.
+3. So sánh target, input và had_auth tại exact_replay.
+4. Phân biệt các pha exact_replay, neighbor_probe, coverage_mutation.
+5. Kiểm tra cách bỏ qua report thiếu had_auth; không đoán token/quyền.
+6. Nếu chạy --concolic riêng, dùng seed_order_valid.json và trace các nhánh totalAmount, không mô tả đây là replay đầy đủ ngữ cảnh blackbox.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Khảo sát coverage giữ input và trạng thái bật/tắt xác thực ở lần đầu; không cam kết cùng token/ID hoặc lịch sử dữ liệu. Không tái hiện từ dữ liệu sạch phải ghi khác biệt trạng thái, không tự bác bỏ phát hiện. Coverage và lân cận không được trình bày thành symbolic execution. Concolic báo cáo riêng model, trace và tiền tố nhánh được xác nhận.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="409" customHeight="1" s="6">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-21</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-FUZZ-21</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra quy trình fuzzing: Khảo sát giá trị số quanh input gây lỗi</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Có input orders bất thường với trường số hữu hạn x; cùng catalog, actor, phí/giảm giá và trạng thái seed ở mỗi lượt; công cụ khảo sát chạy độc lập.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>1. Lưu input gốc x và triệu chứng.
+2. Giữ các trường khác, thử x-1, x, x+1 và 0 từ trạng thái sạch; đổi một trường mỗi lượt.
+3. Lặp lại ba lần từng điểm có triệu chứng.
+4. Lưu HTTP, dữ liệu cuối, timeout, coverage nếu có; đối chiếu oracle nghiệp vụ và lỗi tiến trình riêng.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Có bảng điểm đã thử và triệu chứng từng điểm. HTTP 500 chỉ ghi lỗi ứng dụng, không ghi memory crash. Chỉ báo miền đã khảo sát; chưa được nhận biên nhỏ nhất/lớn nhất hay tính đơn điệu nếu chưa chứng minh.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="409" customHeight="1" s="6">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-8</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-FIX-parse_discount_code</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Hàm sinh mã C: parse_discount_code (buffer-overflow)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu C parse_discount_code, lỗi cấy buffer-overflow; có driver gọi hàm, compiler và AddressSanitizer hoạt động. Phạm vi native fixture, không phải API Node.js.
+Chỉ chạy trên hàm C minh họa độc lập; cần compiler và instrumentation phù hợp. Không phải đường thực thi native đã xác nhận của API Node.js.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>1. Sinh mã C và chạy kiểm tra tĩnh như testcase gốc.
+2. Tạo driver gọi parse_discount_code, biên dịch -g -O0 và instrumentation phù hợp; kiểm tra đối chứng công cụ.
+3. Chạy chuỗi ASCII dài B-1, B, B+1 với B=32 byte và đối chứng ngắn.
+4. Lưu input, binary/source hash, stderr, exit code/signal và vị trí chẩn đoán.
+5. Tái hiện từ tiến trình sạch; chạy đối chứng an toàn cùng input.
+Chạy cả mẫu lỗi cấy và đối chứng an toàn trên cùng input; lưu input, build flags, stderr, mã thoát và vị trí lỗi; lặp lại input gây lỗi.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng an toàn không có chẩn đoán buffer-overflow; mẫu lỗi cấy phải có chẩn đoán buffer-overflow tại hàm mục tiêu từ AddressSanitizer hoặc công cụ phát hiện lỗi bộ nhớ tương đương. Mẫu lỗi bị phát hiện là xác nhận đối chứng công cụ, không phải ứng dụng đã an toàn. Thiếu công cụ/bằng chứng: chưa xác minh. Không dùng HTTP 500 làm bằng chứng; leak không bắt buộc làm tiến trình crash.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="409" customHeight="1" s="6">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-FIX-write_order_transaction_log</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Hàm sinh mã C: write_order_transaction_log (memory-leak)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu C write_order_transaction_log, lỗi cấy memory-leak; có driver gọi hàm, compiler và LeakSanitizer hoặc công cụ kiểm tra leak tương đương hoạt động. Phạm vi native fixture, không phải API Node.js.
+Chỉ chạy trên hàm C minh họa độc lập; cần compiler và instrumentation phù hợp. Không phải đường thực thi native đã xác nhận của API Node.js.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>1. Sinh mã C và chạy kiểm tra tĩnh như testcase gốc.
+2. Tạo driver gọi write_order_transaction_log, biên dịch -g -O0 và instrumentation phù hợp; kiểm tra đối chứng công cụ.
+3. Chạy đường thực thi hàm một lần trên mỗi tiến trình mới; có đối chứng đã sửa tương ứng.
+4. Lưu input, binary/source hash, stderr, exit code/signal và vị trí chẩn đoán.
+5. Tái hiện từ tiến trình sạch; chạy đối chứng an toàn cùng input.
+Chạy cả mẫu lỗi cấy và đối chứng an toàn trên cùng input; lưu input, build flags, stderr, mã thoát và vị trí lỗi; lặp lại input gây lỗi.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng an toàn không có chẩn đoán memory-leak; mẫu lỗi cấy phải có chẩn đoán memory-leak tại hàm mục tiêu từ LeakSanitizer hoặc công cụ phát hiện leak tương đương. Mẫu lỗi bị phát hiện là xác nhận đối chứng công cụ, không phải ứng dụng đã an toàn. Thiếu công cụ/bằng chứng: chưa xác minh. Không dùng HTTP 500 làm bằng chứng; leak không bắt buộc làm tiến trình crash.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="409" customHeight="1" s="6">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-FIX-close_order_checkout_session</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Hàm sinh mã C: close_order_checkout_session (double-free)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu C close_order_checkout_session, lỗi cấy double-free; có driver gọi hàm, compiler và AddressSanitizer hoạt động. Phạm vi native fixture, không phải API Node.js.
+Chỉ chạy trên hàm C minh họa độc lập; cần compiler và instrumentation phù hợp. Không phải đường thực thi native đã xác nhận của API Node.js.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>1. Sinh mã C và chạy kiểm tra tĩnh như testcase gốc.
+2. Tạo driver gọi close_order_checkout_session, biên dịch -g -O0 và instrumentation phù hợp; kiểm tra đối chứng công cụ.
+3. Chạy đường thực thi hàm một lần trên mỗi tiến trình mới; có đối chứng đã sửa tương ứng.
+4. Lưu input, binary/source hash, stderr, exit code/signal và vị trí chẩn đoán.
+5. Tái hiện từ tiến trình sạch; chạy đối chứng an toàn cùng input.
+Chạy cả mẫu lỗi cấy và đối chứng an toàn trên cùng input; lưu input, build flags, stderr, mã thoát và vị trí lỗi; lặp lại input gây lỗi.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng an toàn không có chẩn đoán double-free; mẫu lỗi cấy phải có chẩn đoán double-free tại hàm mục tiêu từ AddressSanitizer hoặc công cụ phát hiện lỗi bộ nhớ tương đương. Mẫu lỗi bị phát hiện là xác nhận đối chứng công cụ, không phải ứng dụng đã an toàn. Thiếu công cụ/bằng chứng: chưa xác minh. Không dùng HTTP 500 làm bằng chứng; leak không bắt buộc làm tiến trình crash.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="409" customHeight="1" s="6">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-FIX-release_cart_cache_buffer</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Hàm sinh mã C: release_cart_cache_buffer (use-after-free)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu C release_cart_cache_buffer, lỗi cấy use-after-free; có driver gọi hàm, compiler và AddressSanitizer hoạt động. Phạm vi native fixture, không phải API Node.js.
+Chỉ chạy trên hàm C minh họa độc lập; cần compiler và instrumentation phù hợp. Không phải đường thực thi native đã xác nhận của API Node.js.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>1. Sinh mã C và chạy kiểm tra tĩnh như testcase gốc.
+2. Tạo driver gọi release_cart_cache_buffer, biên dịch -g -O0 và instrumentation phù hợp; kiểm tra đối chứng công cụ.
+3. Chạy đường thực thi hàm một lần trên mỗi tiến trình mới; có đối chứng đã sửa tương ứng.
+4. Lưu input, binary/source hash, stderr, exit code/signal và vị trí chẩn đoán.
+5. Tái hiện từ tiến trình sạch; chạy đối chứng an toàn cùng input.
+Chạy cả mẫu lỗi cấy và đối chứng an toàn trên cùng input; lưu input, build flags, stderr, mã thoát và vị trí lỗi; lặp lại input gây lỗi.</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng an toàn không có chẩn đoán use-after-free; mẫu lỗi cấy phải có chẩn đoán use-after-free tại hàm mục tiêu từ AddressSanitizer hoặc công cụ phát hiện lỗi bộ nhớ tương đương. Mẫu lỗi bị phát hiện là xác nhận đối chứng công cụ, không phải ứng dụng đã an toàn. Thiếu công cụ/bằng chứng: chưa xác minh. Không dùng HTTP 500 làm bằng chứng; leak không bắt buộc làm tiến trình crash.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="283.2" customHeight="1" s="6">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-9</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-FIX-order_error_rate</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Hàm Python: order_error_rate chia cho 0</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Đã sinh mã Python Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
+2. Chạy blackbox_fuzz() với total_orders=0
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Chấp nhận với totalAmount âm (200) - VI PHẠM, đã được white-box fuzzer xác nhận</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="344.8" customHeight="1" s="6">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu lỗi cấy phát sinh ZeroDivisionError với input chia cho 0; lưu traceback, input và cách gọi. Đối chứng an toàn xử lý trường hợp này có kiểm soát. Ngoại lệ Python chưa chứng minh crash server hoặc lỗi bộ nhớ native; thiếu thực thi thì chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="344.8" customHeight="1" s="6">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>TC-ORD-7</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>REQ-ORD-7, NFR-ORD-4</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Sử dụng discountCode ĐỒNG THỜI (race)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Đã đăng nhập, có token, mã SALE10 chưa dùng</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Gửi 2 request tạo đơn hàng CÙNG discountCode=SALE10 ĐỒNG THỜI (không tuần tự)
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>MONG ĐỢI: chỉ 1 trong 2 thành công. CHƯA được kiểm chứng bởi 2 fuzzer hiện có (chỉ test tuần tự, đã xác nhận tuần tự hoạt động đúng: lần2=400)</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="267.8" customHeight="1" s="6">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>TC-ORD-8</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>REQ-ORD-FIX-parse_discount_code</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Hàm sinh mã C: parse_discount_code (buffer-overflow)</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã C Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy check_c_source()
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Phát hiện CWE-120</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="283.2" customHeight="1" s="6">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>TC-ORD-9</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>REQ-ORD-FIX-order_error_rate</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Hàm Python: order_error_rate chia cho 0</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã Python Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy blackbox_fuzz() với total_orders=0
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Tìm được crash ZeroDivisionError (CWE-248)</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="283.2" customHeight="1" s="6">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Với discountCode dùng một lần và hai request thực sự đồng thời, chỉ một request áp dụng mã thành công; kiểm tra cả dữ liệu lưu. Lưu lịch gửi/nhận để xác nhận đồng thời; chạy tuần tự chưa chứng minh không có race.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="283.2" customHeight="1" s="6">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>TC-ORD-10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>REQ-ORD-SMT-total_order_value_counter</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: total_order_value_counter</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT (có thể tràn số)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="283.2" customHeight="1" s="6">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>TC-ORD-11</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>REQ-ORD-FIX-write_order_transaction_log</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Hàm sinh mã C: write_order_transaction_log (memory-leak)</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã C cho hàm write_order_transaction_log Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy check_c_source() trên mã sinh ra
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Phát hiện thiếu free() tương ứng với malloc() (memory-leak, CWE-401)</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="283.2" customHeight="1" s="6">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>TC-ORD-12</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>REQ-ORD-FIX-close_order_checkout_session</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Hàm sinh mã C: close_order_checkout_session (double-free)</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã C cho hàm close_order_checkout_session Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy check_c_source() trên mã sinh ra
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Phát hiện free() được gọi 2 lần trên cùng 1 con trỏ (double-free, CWE-415)</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="283.2" customHeight="1" s="6">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>TC-ORD-13</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>REQ-ORD-FIX-release_cart_cache_buffer</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Hàm sinh mã C: release_cart_cache_buffer (use-after-free)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã C cho hàm release_cart_cache_buffer Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy check_c_source() trên mã sinh ra
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Phát hiện vùng nhớ được truy cập SAU khi đã free() (use-after-free, CWE-416)</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="360.2" customHeight="1" s="6">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="18" ht="360.2" customHeight="1" s="6">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>TC-ORD-14</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>REQ-ORD-SMT-daily_order_counter</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: daily_order_counter</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT tương ứng cho dòng 'daily_order_counter' Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3 trên BieuThucTran của dòng 'daily_order_counter'
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT (vẫn có thể tràn số nếu chỉ dùng kiểu dữ liệu hẹp như giả định nghiệp vụ)</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="375.6" customHeight="1" s="6">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="19" ht="375.6" customHeight="1" s="6">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>TC-ORD-15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>REQ-ORD-SMT-concurrent_discount_redeem_counter</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: concurrent_discount_redeem_counter</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT tương ứng cho dòng 'concurrent_discount_redeem_counter' Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3 trên BieuThucTran của dòng 'concurrent_discount_redeem_counter'
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT (vẫn có thể tràn số nếu chỉ dùng kiểu dữ liệu hẹp như giả định nghiệp vụ)</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="375.6" customHeight="1" s="6">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="20" ht="375.6" customHeight="1" s="6">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TC-ORD-16</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>REQ-ORD-SMT-active_discount_code_counter</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: active_discount_code_counter</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT tương ứng cho dòng 'active_discount_code_counter' Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3 trên BieuThucTran của dòng 'active_discount_code_counter'
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT (vẫn có thể tràn số nếu chỉ dùng kiểu dữ liệu hẹp như giả định nghiệp vụ)</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="360.2" customHeight="1" s="6">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="21" ht="360.2" customHeight="1" s="6">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>TC-ORD-17</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>REQ-ORD-SMT-order_crash_counter</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: order_crash_counter</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT tương ứng cho dòng 'order_crash_counter' Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3 trên BieuThucTran của dòng 'order_crash_counter'
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT (vẫn có thể tràn số nếu chỉ dùng kiểu dữ liệu hẹp như giả định nghiệp vụ)</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="375.6" customHeight="1" s="6">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>TC-ORD-18</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>REQ-ORD-5</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Giá và tổng tiền giả nhưng tự khớp nhau</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Catalog productId=1 có giá 200000; actor hợp lệ. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>1. Gửi sản phẩm price=1, quantity=2, totalAmount=2; đọc giá trị đơn đã lưu nếu thành công.
-2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
-Dữ liệu thử: {"products":[{"productId":1,"price":1,"quantity":2}],"totalAmount":2}</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Từ chối 400/422 hoặc tính lại 400000 khi không có phí/giảm giá. Không lưu tổng 2.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="344.8" customHeight="1" s="6">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22" ht="344.8" customHeight="1" s="6">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>TC-ORD-19</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>REQ-ORD-2, REQ-ORD-5, REQ-ORD-8</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Tạo đơn hợp lệ làm mẫu đối chứng</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng seed hợp lệ trước khi đột biến đơn hàng</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>User hợp lệ; sản phẩm còn hàng; giá catalog tin cậy. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>1. Gửi giỏ hàng và giao hàng hợp lệ; đọc đơn lưu và đối chiếu catalog.
 2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
-Dữ liệu thử: Seed order hợp lệ, không voucher/phí; quantity=2, giá catalog=200000.</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>200/201; đơn lưu đúng user/sản phẩm/số lượng; tổng 400000.</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+Dữ liệu thử: Seed order hợp lệ, không voucher/phí; quantity=2, giá catalog=200000.
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200/201; đơn có đúng user, sản phẩm, số lượng và tổng 400000 của seed. Seed không chạy được thì không quy lỗi cho input đột biến.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-22</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-DISCOVERY</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Khám phá lỗi runtime chưa biết bằng seed và mutation có ngân sách</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: JWT → giỏ hàng → giao hàng → coupon → lưu đơn → tác vụ sau lưu. Trạng thái sạch: seed_order_valid.json; user/token hợp lệ, catalog giá/tồn kho cố định, mã giảm giá chưa dùng. Có runner cô lập và giới hạn thời gian mỗi lượt, số lượt, kích thước input, CPU/RAM. Có seed đối chứng chạy được.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Reset trạng thái, chạy seed đối chứng và xác nhận tới target. 2. Đột biến products và phần tử lồng, shippingInfo, discountCode, totalAmount; số phần tử, độ dài byte, sai kiểu; trộn mutation có cấu trúc và byte-level khi parser/driver hỗ trợ. 3. Chốt random seed=7, ngân sách 1000 input mới, tối đa 64 KiB/input, timeout mỗi target=2 giây sau setup; điều chỉnh có ghi lý do trước chạy nếu đối chứng không đáp ứng. 4. Chạy nhiều random seed độc lập; lưu toàn bộ input có triệu chứng và corpus mở coverage nếu có. Không hardcode input lỗi duy nhất. 5. Reset từng lượt hoặc lưu đầy đủ prefix trạng thái với target stateful. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Seed đối chứng tới đúng target. Lưu input mới và triệu chứng thực đo; không có lỗi trong ngân sách chỉ ghi NOT_FOUND_WITHIN_BUDGET, không chứng minh an toàn. HTTP 5xx là lỗi ứng dụng, không tự là crash/bộ nhớ. Thiếu runner/giám sát: NOT_IMPLEMENTED hoặc INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-23</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-MEMORY</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Khám phá truy cập bộ nhớ sai bằng target native instrumented</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: JWT → giỏ hàng → giao hàng → coupon → lưu đơn → tác vụ sau lưu. Trạng thái sạch: seed_order_valid.json; user/token hợp lệ, catalog giá/tồn kho cố định, mã giảm giá chưa dùng. Có mã C/C++ hoặc native dependency thực có driver nhận input; compiler và ASan (hoặc công cụ tương đương) hoạt động. Nếu chỉ có API JS thì chưa đáp ứng điều kiện này.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Xác định target native và đường gọi; nếu dùng hàm HamSinhMa phải ghi là fixture độc lập. 2. Build có debug symbols và instrumentation; chạy đối chứng an toàn và mẫu lỗi biết trước để xác nhận công cụ. 3. Dùng seed hợp lệ rồi fuzz products và phần tử lồng, shippingInfo, discountCode, totalAmount; số phần tử, độ dài byte, sai kiểu; thử B-1/B/B+1 theo BYTE, tính cả NUL khi dùng chuỗi C. 4. Thu chẩn đoán out-of-bounds/use-after-free/double-free, stack và allocation/free stack nếu công cụ cung cấp. 5. Replay input từ tiến trình sạch ba lần và đối chiếu mẫu đã sửa. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ xác nhận loại lỗi khi diagnostic chỉ vào thao tác bộ nhớ sai trong binary mục tiêu. Crash đơn thuần không xác định loại lỗi bộ nhớ; ASan không bảo đảm phát hiện mọi lỗi. Đối chứng lỗi cấy được phát hiện chỉ xác nhận công cụ, không phải phát hiện production. Thiếu instrumentation/driver: chưa đánh giá.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-24</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-LEAK</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra rò rỉ cấp phát và tăng trưởng bộ nhớ qua vòng đời thao tác</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: JWT → giỏ hàng → giao hàng → coupon → lưu đơn → tác vụ sau lưu. Trạng thái sạch: seed_order_valid.json; user/token hợp lệ, catalog giá/tồn kho cố định, mã giảm giá chưa dùng. Có driver native với LSan/công cụ leak tương đương hoặc profiler heap cho Node; có warmup, đối chứng an toàn và cấu hình tài nguyên cố định.</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Làm nóng bằng 100 thao tác hợp lệ. 2. Reset và chạy ba batch độc lập, mỗi batch 1000 thao tác từ seed/mutation có giới hạn. 3. Với native, thu leak report và allocation stack khi kết thúc bình thường; không chỉ kill timeout. 4. Với Node, chụp heap trước/sau cùng điều kiện GC, truy vết retaining path và ownership; tách dữ liệu nghiệp vụ cố ý giữ trong datastore khỏi rò rỉ. 5. So sánh đối chứng đã giải phóng tài nguyên; ghi RSS/heap theo thời gian. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Native leak cần chẩn đoán allocation không được thu hồi; retention Node cần chứng minh đối tượng hết vòng đời vẫn bị giữ ngoài thiết kế. RAM/RSS tăng, GC trễ hoặc Map lưu thêm đơn hợp lệ chưa đủ kết luận leak. OOM phải phân loại riêng và chưa tự chứng minh leak; thiếu công cụ: INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-25</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-CRASH_HANG</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Giám sát và phân biệt crash, timeout, hang, OOM và lỗi ứng dụng</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: JWT → giỏ hàng → giao hàng → coupon → lưu đơn → tác vụ sau lưu. Trạng thái sạch: seed_order_valid.json; user/token hợp lệ, catalog giá/tồn kho cố định, mã giảm giá chưa dùng. Có supervisor quan sát đúng target PID, handshake READY, health probe và fixture nhanh/crash/chờ độc lập; không dùng tiến trình production.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Chạy đối chứng nhanh, HTTP 500 còn sống, kết thúc bình thường, crash có chủ đích và fixture chờ. 2. Bắt đầu timeout 2 giây sau READY; tách thời gian startup/setup. 3. Khi quá hạn, ghi target còn sống, probe/liveness và log trước khi cleanup. 4. Phân biệt target tự dừng với supervisor terminate/kill và hết giới hạn tài nguyên. 5. Replay cùng input/prefix ba tiến trình sạch; loại trừ sai cổng, kết nối, setup và tải máy. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 500 còn sống=APPLICATION_HTTP_ERROR; quá hạn=SUSPECTED_HANG, chỉ xác nhận hang khi lặp có kiểm soát và có quan sát tiến trình. Crash cần bằng chứng target dừng bất thường, không do cleanup; exit khác 0 do validation/sanitizer phải có phân loại nguyên nhân. OOM cần diagnostic/giới hạn tài nguyên, không tự là memory corruption. Đối chứng không được phân loại nhầm; thiếu bằng chứng=INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-26</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-REPLAY</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Tái hiện input runtime với trạng thái ban đầu và prefix đầy đủ</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: JWT → giỏ hàng → giao hàng → coupon → lưu đơn → tác vụ sau lưu. Trạng thái sạch: seed_order_valid.json; user/token hợp lệ, catalog giá/tồn kho cố định, mã giảm giá chưa dùng. Có artifact của input phát hiện trong lượt khám phá; có snapshot/reset và build tương ứng. Không có finding thì ghi NO_CANDIDATE.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Đọc artifact, khôi phục build/config, dữ liệu và actor; ánh xạ ID/token test mới theo vai trò. 2. Chạy seed đối chứng. 3. Replay input độc lập và replay cùng prefix đã ghi, mỗi chế độ ba lần từ tiến trình sạch. 4. So sánh diagnostic, stack chuẩn hóa, exit/liveness và trạng thái sau cùng; ghi tỷ lệ tái hiện. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ ghi tái hiện xác nhận khi cùng loại triệu chứng và bằng chứng mục tiêu lặp lại; lỗi setup/version không được thay cho lỗi gốc. Không tái hiện phải giữ artifact và ghi NOT_REPRODUCED/STATE_DEPENDENT/INCONCLUSIVE theo bằng chứng; không tự bác bỏ phát hiện.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TC-ORD-27</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-MINIMIZE</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Thu nhỏ input và nhóm phát hiện runtime theo chữ ký bằng chứng</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: JWT → giỏ hàng → giao hàng → coupon → lưu đơn → tác vụ sau lưu. Trạng thái sạch: seed_order_valid.json; user/token hợp lệ, catalog giá/tồn kho cố định, mã giảm giá chưa dùng. Có finding đã replay; có oracle giữ nguyên loại lỗi/stack mục tiêu, reset sạch và ngân sách tối đa 200 phép thử giảm; giữ artifact gốc bất biến.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Giảm trường, độ dài byte, phần tử mảng hoặc prefix từng bước. 2. Mỗi ứng viên chạy sạch, giữ lại chỉ khi còn cùng diagnostic/stack mục tiêu. 3. Dừng khi hết ngân sách hoặc không giảm thêm, replay bản nhỏ ba lần. 4. Nhóm theo target/build, loại lỗi và stack chuẩn hóa; loại địa chỉ ngẫu nhiên, giữ function/source location. 5. Liên kết input gốc, input giảm và lịch sử thử; hang dùng chữ ký liveness/prefix riêng. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Bản giảm phải giữ triệu chứng gốc, không chuyển từ lỗi bộ nhớ sang validation/setup. Chỉ gọi là đã giảm trong ngân sách, không khẳng định nhỏ nhất toàn cục. Nhóm chữ ký là ứng viên cùng nguyên nhân, không chứng minh số lỗi gốc; số occurrences báo cáo riêng. Không có finding=NO_CANDIDATE.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1296,7 +1733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="2" min="1" max="1"/>
@@ -1372,7 +1809,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36.8" customHeight="1" s="6">
+    <row r="4" ht="120" customHeight="1" s="6">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>REQ-ORD-3</t>
@@ -1380,7 +1817,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Thiếu totalAmount phải trả về HTTP 400, không được để rơi xuống HTTP 500</t>
+          <t>totalAmount bắt buộc có mặt và không null; thiếu hoặc null phải bị từ chối HTTP 400 có kiểm soát, không để phát sinh HTTP 500 do lỗi required ở tầng lưu trữ.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1394,7 +1831,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="67.59999999999999" customHeight="1" s="6">
+    <row r="5" ht="120" customHeight="1" s="6">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>REQ-ORD-4</t>
@@ -1402,7 +1839,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>totalAmount/discountAmount/voucherDiscount/shippingFee sai kiểu dữ liệu không được gây phản hồi HTTP 500 do đầu vào không hợp lệ</t>
+          <t>totalAmount/discountAmount/voucherDiscount/shippingFee khi có mặt phải có kiểu JSON number hữu hạn; không chấp nhận boolean, object, array hoặc chuỗi kể cả chuỗi số bằng cách ép kiểu ngầm. Sai kiểu phải bị từ chối HTTP 400/422, không gây HTTP 500. Campaign hiện có kịch bản sai kiểu totalAmount; concolic chỉ mô hình trường totalAmount, chưa bao phủ đầy đủ ba trường tùy chọn.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1829,6 +2266,182 @@
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1" s="6">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-FUZZ-20</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Luồng blackbox → khảo sát coverage phải giữ target, JSON input và trạng thái xác thực bật/tắt; lượt exact_replay chạy nguyên input trước khi đột biến. Đây là coverage-guided, không thu thập path condition tượng trưng. Concolic --concolic là chiến dịch riêng từ seed đơn hợp lệ, không tự khôi phục chuỗi trạng thái blackbox.</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>functional</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1" s="6">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>REQ-ORD-FUZZ-21</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Khảo sát lân cận phải lưu input và triệu chứng từng điểm; không suy ra toàn bộ khoảng lỗi từ vài mẫu. Chọn input theo line coverage không đồng nghĩa giải path condition bằng SMT hoặc đo branch/edge coverage.</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>functional</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-DISCOVERY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Khám phá lỗi runtime chưa biết bằng seed và mutation có ngân sách. Seed đối chứng tới đúng target. Lưu input mới và triệu chứng thực đo; không có lỗi trong ngân sách chỉ ghi NOT_FOUND_WITHIN_BUDGET, không chứng minh an toàn. HTTP 5xx là lỗi ứng dụng, không tự là crash/bộ nhớ. Thiếu runner/giám sát: NOT_IMPLEMENTED hoặc INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-MEMORY</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Khám phá truy cập bộ nhớ sai bằng target native instrumented. Chỉ xác nhận loại lỗi khi diagnostic chỉ vào thao tác bộ nhớ sai trong binary mục tiêu. Crash đơn thuần không xác định loại lỗi bộ nhớ; ASan không bảo đảm phát hiện mọi lỗi. Đối chứng lỗi cấy được phát hiện chỉ xác nhận công cụ, không phải phát hiện production. Thiếu instrumentation/driver: chưa đánh giá.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-LEAK</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Kiểm tra rò rỉ cấp phát và tăng trưởng bộ nhớ qua vòng đời thao tác. Native leak cần chẩn đoán allocation không được thu hồi; retention Node cần chứng minh đối tượng hết vòng đời vẫn bị giữ ngoài thiết kế. RAM/RSS tăng, GC trễ hoặc Map lưu thêm đơn hợp lệ chưa đủ kết luận leak. OOM phải phân loại riêng và chưa tự chứng minh leak; thiếu công cụ: INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-CRASH_HANG</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Giám sát và phân biệt crash, timeout, hang, OOM và lỗi ứng dụng. HTTP 500 còn sống=APPLICATION_HTTP_ERROR; quá hạn=SUSPECTED_HANG, chỉ xác nhận hang khi lặp có kiểm soát và có quan sát tiến trình. Crash cần bằng chứng target dừng bất thường, không do cleanup; exit khác 0 do validation/sanitizer phải có phân loại nguyên nhân. OOM cần diagnostic/giới hạn tài nguyên, không tự là memory corruption. Đối chứng không được phân loại nhầm; thiếu bằng chứng=INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-REPLAY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Tái hiện input runtime với trạng thái ban đầu và prefix đầy đủ. Chỉ ghi tái hiện xác nhận khi cùng loại triệu chứng và bằng chứng mục tiêu lặp lại; lỗi setup/version không được thay cho lỗi gốc. Không tái hiện phải giữ artifact và ghi NOT_REPRODUCED/STATE_DEPENDENT/INCONCLUSIVE theo bằng chứng; không tự bác bỏ phát hiện.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>REQ-ORD-RUNTIME-MINIMIZE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Thu nhỏ input và nhóm phát hiện runtime theo chữ ký bằng chứng. Bản giảm phải giữ triệu chứng gốc, không chuyển từ lỗi bộ nhớ sang validation/setup. Chỉ gọi là đã giảm trong ngân sách, không khẳng định nhỏ nhất toàn cục. Nhóm chữ ký là ứng viên cùng nguyên nhân, không chứng minh số lỗi gốc; số occurrences báo cáo riêng. Không có finding=NO_CANDIDATE.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2027,7 +2640,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="113.8" customHeight="1" s="6">
+    <row r="4" ht="120" customHeight="1" s="6">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>CON-ORD-3</t>
@@ -2035,7 +2648,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Các trường tiền phải là số hữu hạn; trường bắt buộc không được thiếu, trường phí/giảm giá tùy chọn mặc định bằng 0 khi vắng mặt, không dùng truthy để thay validation.</t>
+          <t>Các trường tiền phải có kiểu JSON number hữu hạn; chuỗi số và boolean không phải số theo hợp đồng API, dù datastore có thể ép kiểu. totalAmount bắt buộc có mặt, không null; phí/giảm giá tùy chọn mặc định 0 chỉ khi vắng mặt, không dùng truthy để bỏ qua validation. Concolic dùng các đại diện kiểu, không chứng minh toàn miền số, số thực hoặc mọi chuỗi.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
